--- a/isoReport/docs/solicitudes_2025.xlsx
+++ b/isoReport/docs/solicitudes_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aagricola-my.sharepoint.com/personal/inavarro_atlanticaagricola_com/Documents/Escritorio/Repos/isoReport/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_79891E58154D9C0E62355476585DCE3A87452DBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A55AE70C-D625-44AB-A214-B328AF69EF86}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_79891E58154D9C0E62355476585DCE3A87452DBB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE59DF6-CB04-4B40-98AC-6F5CBE43006D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1846,6 +1846,8 @@
     <col min="12" max="12" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="32" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="110.5546875" style="3" customWidth="1"/>
     <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
